--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10107"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/Notes/Algorithms/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/Mynotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896429C8-E3C3-474C-8A51-F07567AD5092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB8FA17-2D0C-6249-8F5E-279A932562E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="760" windowWidth="28040" windowHeight="15920" activeTab="9" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" firstSheet="8" activeTab="8" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="497">
   <si>
     <t>#</t>
   </si>
@@ -1533,6 +1533,18 @@
   </si>
   <si>
     <t>33 搜索旋转排序数组</t>
+  </si>
+  <si>
+    <t>2302 统计得分小于K的子数组数目</t>
+  </si>
+  <si>
+    <t>815 公交路线</t>
+  </si>
+  <si>
+    <t>502 IPO</t>
+  </si>
+  <si>
+    <t>373 查找和最小的K对数字</t>
   </si>
 </sst>
 </file>
@@ -4532,7 +4544,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3390D82-F280-2841-A652-0961C2865E3C}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.1640625" style="10" customWidth="1"/>
@@ -4848,56 +4860,56 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7">
+        <v>20250625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="7">
+      <c r="B30" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="7">
         <v>20240518</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="7">
-        <v>20220925</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="7">
-        <v>20250506</v>
+        <v>20220925</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="7">
-        <v>20220906</v>
+        <v>20250506</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>5</v>
@@ -4908,7 +4920,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>5</v>
@@ -4919,29 +4931,29 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="7">
-        <v>20250126</v>
+        <v>20220906</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="7">
-        <v>20220906</v>
+        <v>20250126</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>5</v>
@@ -4952,113 +4964,124 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C39" s="7">
-        <v>20220913</v>
+        <v>20220906</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="7">
-        <v>20220923</v>
+        <v>20220913</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="7">
-        <v>20230308</v>
+        <v>20220923</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="7">
-        <v>20230319</v>
+        <v>20230308</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="7">
-        <v>20230415</v>
+        <v>20230319</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C44" s="7">
-        <v>20230429</v>
-      </c>
-      <c r="E44" s="8"/>
+        <v>20230415</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="10">
-        <v>20230623</v>
-      </c>
-      <c r="E45" s="14"/>
+        <v>398</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="7">
+        <v>20230429</v>
+      </c>
+      <c r="E45" s="8"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="10">
-        <v>20240504</v>
-      </c>
+        <v>20230623</v>
+      </c>
+      <c r="E46" s="14"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C47" s="10">
-        <v>20240512</v>
+        <v>20240504</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="10">
+        <v>20240512</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="7">
+      <c r="B49" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="7">
         <v>20250114</v>
       </c>
     </row>
@@ -5068,7 +5091,7 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="https://leetcode.cn/problems/all-paths-from-source-to-target/solution/by-wywy-m-nqp0/" xr:uid="{62AA1BDA-9AEF-1D4E-985F-E4BFC300F9ED}"/>
-    <hyperlink ref="A48" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
+    <hyperlink ref="A49" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.cn/problems/path-with-minimum-effort/solution/1631-zui-xiao-ti-li-xiao-hao-lu-jing-dij-36ok/" xr:uid="{B4E6A033-CD2E-1C4F-A02F-38038DA461CB}"/>
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/path-with-maximum-probability/solution/1514-gai-lu-zui-da-de-lu-jing-dijkstra-b-kh0n/" xr:uid="{8F9369A4-3430-114E-8817-0069A16021C5}"/>
     <hyperlink ref="A6" r:id="rId5" display="https://leetcode.cn/problems/course-schedule-ii/solution/210-ke-cheng-biao-iigraph-by-wywy-m-18nk/" xr:uid="{C7EEFC8F-2387-F14A-B36C-A22ACD69ECCB}"/>
@@ -5084,33 +5107,34 @@
     <hyperlink ref="A20" r:id="rId15" display="https://leetcode.cn/problems/01-matrix/solution/-by-wywy-m-1ak4/" xr:uid="{AC1F76FF-A2DA-694F-A769-2136BC16C971}"/>
     <hyperlink ref="A24" r:id="rId16" display="https://leetcode.cn/problems/sliding-puzzle/solution/773-hua-dong-mi-ti-bfs-by-ywrx-c74s/" xr:uid="{0AD32694-5038-3D45-918C-C400FC7946DE}"/>
     <hyperlink ref="A21" r:id="rId17" display="https://leetcode.cn/problems/open-the-lock/solution/752-da-kai-zhuan-pan-suo-bfs-by-ywrx-y6lu/" xr:uid="{479482D9-B268-4348-9013-D7B5073218A6}"/>
-    <hyperlink ref="A39" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
-    <hyperlink ref="A40" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
-    <hyperlink ref="A31" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
-    <hyperlink ref="A32" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
-    <hyperlink ref="A33" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
-    <hyperlink ref="A34" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
-    <hyperlink ref="A35" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
-    <hyperlink ref="A36" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
-    <hyperlink ref="A37" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
-    <hyperlink ref="A38" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
-    <hyperlink ref="A41" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
-    <hyperlink ref="A42" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
+    <hyperlink ref="A40" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
+    <hyperlink ref="A41" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
+    <hyperlink ref="A32" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
+    <hyperlink ref="A33" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
+    <hyperlink ref="A34" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
+    <hyperlink ref="A35" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
+    <hyperlink ref="A36" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
+    <hyperlink ref="A37" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
+    <hyperlink ref="A38" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
+    <hyperlink ref="A39" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
+    <hyperlink ref="A42" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
+    <hyperlink ref="A43" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
     <hyperlink ref="A23" r:id="rId29" xr:uid="{F7F1BE06-524D-3F45-A6A1-43D1A4059E77}"/>
     <hyperlink ref="A9" r:id="rId30" xr:uid="{0E22DCEF-0BC9-3444-97D4-2AB1C84A8351}"/>
     <hyperlink ref="A10" r:id="rId31" xr:uid="{287B3E6D-9056-694F-B287-0EF92D0296AA}"/>
-    <hyperlink ref="A43" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
+    <hyperlink ref="A44" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
     <hyperlink ref="A25" r:id="rId33" xr:uid="{ED5D89E9-76CF-A048-BD72-F0BA151EEC9F}"/>
-    <hyperlink ref="A44" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
-    <hyperlink ref="A45" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
+    <hyperlink ref="A45" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
+    <hyperlink ref="A46" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
     <hyperlink ref="A11" r:id="rId36" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
-    <hyperlink ref="A46" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
+    <hyperlink ref="A47" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
     <hyperlink ref="A26" r:id="rId38" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
-    <hyperlink ref="A47" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
+    <hyperlink ref="A48" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
     <hyperlink ref="A27" r:id="rId40" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
-    <hyperlink ref="A29" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
+    <hyperlink ref="A30" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
     <hyperlink ref="A14" r:id="rId42" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
     <hyperlink ref="A28" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
+    <hyperlink ref="A29" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5998,10 +6022,10 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB69C234-EDE8-3643-8B34-F99DBD5F82C4}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.1640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="61.1640625" style="6" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="6"/>
     <col min="3" max="3" width="16.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="6"/>
@@ -6104,6 +6128,17 @@
       </c>
       <c r="C9" s="7">
         <v>20250302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>20250624</v>
       </c>
     </row>
   </sheetData>
@@ -6119,6 +6154,7 @@
     <hyperlink ref="A7" r:id="rId6" xr:uid="{F73058DF-2D70-FC4B-A90C-750B0201ACF4}"/>
     <hyperlink ref="A8" r:id="rId7" xr:uid="{EEA515CB-0B51-9341-B7AB-1571503CF985}"/>
     <hyperlink ref="A9" r:id="rId8" xr:uid="{032AACC1-B2DF-D24E-9D8A-5897213CA1E6}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{A93CF123-1362-5B4B-B3D9-13A099D7C99B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -9420,7 +9456,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAA87E2-0C96-3045-BD9E-C5C85205F434}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.33203125" style="6" customWidth="1"/>
@@ -9581,6 +9617,28 @@
       </c>
       <c r="C14" s="6">
         <v>20250126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>20250629</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="6">
+        <v>20250629</v>
       </c>
     </row>
   </sheetData>
@@ -9601,6 +9659,8 @@
     <hyperlink ref="A12" r:id="rId11" xr:uid="{54E7FF01-2E95-6B4D-ACCE-9A53C5D09AFB}"/>
     <hyperlink ref="A13" r:id="rId12" xr:uid="{3FBE9858-3DC4-E341-A93C-DE0DF6DD956F}"/>
     <hyperlink ref="A14" r:id="rId13" xr:uid="{8B97E3E3-F60B-A64D-BFFC-2C4D92E1EACE}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{3D86F3EA-BD46-4F47-93AA-0882C9D9D61F}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{CBFBF69D-7CE2-0943-91D7-4BB1286A5EDC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/Notes/Algorithms/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896429C8-E3C3-474C-8A51-F07567AD5092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05175F99-8E6D-C644-9BEE-76BA06791E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="760" windowWidth="28040" windowHeight="15920" activeTab="9" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/Mynotes/Algorithms/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB8FA17-2D0C-6249-8F5E-279A932562E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2285044-229E-294D-9A62-C8D1D5FA3358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" firstSheet="8" activeTab="8" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" firstSheet="8" activeTab="15" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -5379,7 +5379,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="7">
-        <v>20230219</v>
+        <v>20250709</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2285044-229E-294D-9A62-C8D1D5FA3358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E8D2C6-F459-6B48-A8F2-09B7EC0A0956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" firstSheet="8" activeTab="15" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" activeTab="8" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="501">
   <si>
     <t>#</t>
   </si>
@@ -1545,6 +1545,18 @@
   </si>
   <si>
     <t>373 查找和最小的K对数字</t>
+  </si>
+  <si>
+    <t>38 外观数列</t>
+  </si>
+  <si>
+    <t>43 字符串相乘</t>
+  </si>
+  <si>
+    <t>63 不同路径II</t>
+  </si>
+  <si>
+    <t>277 搜寻名人</t>
   </si>
 </sst>
 </file>
@@ -2846,7 +2858,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF52CBDF-A54F-B64B-ABC7-BC9DA66EFACF}">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" style="10" customWidth="1"/>
@@ -3590,6 +3602,17 @@
       </c>
       <c r="C67" s="10">
         <v>20250117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="10">
+        <v>20250713</v>
       </c>
     </row>
   </sheetData>
@@ -3653,6 +3676,7 @@
     <hyperlink ref="A66" r:id="rId54" xr:uid="{9B0B48BB-15C1-1349-B1E8-B625E5144562}"/>
     <hyperlink ref="A67" r:id="rId55" xr:uid="{A77FFA44-1F03-2D4A-AD88-E7428C9AA2D5}"/>
     <hyperlink ref="A8" r:id="rId56" display="https://leetcode.cn/problems/unique-paths/solutions/3057839/62-bu-tong-lu-jing-dp-by-ywrx-rh78/" xr:uid="{46A1A02C-4549-4046-98BB-52A767D35641}"/>
+    <hyperlink ref="A68" r:id="rId57" xr:uid="{E80A8A71-063F-A44D-8B00-EB348F17438D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3831,7 +3855,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="7">
-        <v>20220911</v>
+        <v>20250713</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -4544,7 +4568,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3390D82-F280-2841-A652-0961C2865E3C}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.1640625" style="10" customWidth="1"/>
@@ -4663,196 +4687,196 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7">
+        <v>20250713</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
         <v>20250117</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="7">
-        <v>20240505</v>
-      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="7">
-        <v>20250502</v>
+        <v>20240505</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="7">
-        <v>20220612</v>
+        <v>20250502</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="7">
-        <v>20220912</v>
+        <v>20220612</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="7">
-        <v>20220914</v>
+        <v>20220912</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="7">
-        <v>20250506</v>
+        <v>20220914</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="7">
-        <v>20220926</v>
+        <v>20250506</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="7">
-        <v>20221020</v>
+        <v>20220926</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="7">
-        <v>20230220</v>
+        <v>20221020</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C22" s="7">
-        <v>20240512</v>
+        <v>20230220</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>346</v>
+        <v>230</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="7">
-        <v>20230324</v>
+        <v>20240512</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>232</v>
+        <v>346</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="7">
-        <v>20230220</v>
+        <v>20230324</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>397</v>
+        <v>232</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="7">
-        <v>20250513</v>
+        <v>20230220</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>20240507</v>
+        <v>20250513</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C27" s="7">
-        <v>20250506</v>
+        <v>20240507</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>486</v>
+        <v>5</v>
       </c>
       <c r="C28" s="7">
         <v>20250506</v>
@@ -4860,67 +4884,67 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C29" s="7">
-        <v>20250625</v>
+        <v>20250506</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="7">
+        <v>20250625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="7">
+      <c r="B31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="7">
         <v>20240518</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="7">
-        <v>20220925</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="7">
-        <v>20250506</v>
+        <v>20220925</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="7">
-        <v>20220906</v>
+        <v>20250506</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>5</v>
@@ -4931,7 +4955,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>5</v>
@@ -4942,29 +4966,29 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="7">
-        <v>20250126</v>
+        <v>20220906</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="7">
-        <v>20220906</v>
+        <v>20250126</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>5</v>
@@ -4975,166 +4999,178 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C40" s="7">
-        <v>20220913</v>
+        <v>20220906</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="7">
-        <v>20220923</v>
+        <v>20220913</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="7">
-        <v>20230308</v>
+        <v>20220923</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="7">
-        <v>20230319</v>
+        <v>20230308</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="7">
-        <v>20230415</v>
+        <v>20230319</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C45" s="7">
-        <v>20230429</v>
-      </c>
-      <c r="E45" s="8"/>
+        <v>20230415</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="10">
-        <v>20230623</v>
-      </c>
-      <c r="E46" s="14"/>
+        <v>398</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="7">
+        <v>20230429</v>
+      </c>
+      <c r="E46" s="8"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="10">
-        <v>20240504</v>
-      </c>
+        <v>20230623</v>
+      </c>
+      <c r="E47" s="14"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C48" s="10">
-        <v>20240512</v>
+        <v>20240504</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="10">
+        <v>20240512</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="7">
+      <c r="B50" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="7">
         <v>20250114</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:C24">
-    <sortCondition ref="B13:B24" customList="E,M,H"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:C25">
+    <sortCondition ref="B14:B25" customList="E,M,H"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="https://leetcode.cn/problems/all-paths-from-source-to-target/solution/by-wywy-m-nqp0/" xr:uid="{62AA1BDA-9AEF-1D4E-985F-E4BFC300F9ED}"/>
-    <hyperlink ref="A49" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
+    <hyperlink ref="A50" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.cn/problems/path-with-minimum-effort/solution/1631-zui-xiao-ti-li-xiao-hao-lu-jing-dij-36ok/" xr:uid="{B4E6A033-CD2E-1C4F-A02F-38038DA461CB}"/>
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/path-with-maximum-probability/solution/1514-gai-lu-zui-da-de-lu-jing-dijkstra-b-kh0n/" xr:uid="{8F9369A4-3430-114E-8817-0069A16021C5}"/>
     <hyperlink ref="A6" r:id="rId5" display="https://leetcode.cn/problems/course-schedule-ii/solution/210-ke-cheng-biao-iigraph-by-wywy-m-18nk/" xr:uid="{C7EEFC8F-2387-F14A-B36C-A22ACD69ECCB}"/>
     <hyperlink ref="A7" r:id="rId6" display="https://leetcode.cn/problems/network-delay-time/solution/743-wang-luo-yan-chi-shi-jian-dijkstra-b-6zyo/" xr:uid="{FC2F7E70-70B6-EC40-83E9-F14EEDE1A2B2}"/>
     <hyperlink ref="A8" r:id="rId7" display="https://leetcode.cn/problems/min-cost-to-connect-all-points/solution/1584-lian-jie-suo-you-dian-de-zui-xiao-f-dtmy/" xr:uid="{D6E252E8-6A56-B449-917D-D9191B43E8F1}"/>
-    <hyperlink ref="A13" r:id="rId8" display="https://leetcode-cn.com/problems/shortest-path-in-binary-matrix/solution/1091-er-jin-zhi-ju-zhen-zui-duan-lu-jing-00dr/" xr:uid="{678CC0D2-5BB2-9447-A9D9-85A1922DAD7A}"/>
-    <hyperlink ref="A15" r:id="rId9" display="https://leetcode.cn/problems/ji-qi-ren-de-yun-dong-fan-wei-lcof/solution/-by-wywy-m-hks2/" xr:uid="{433B27C5-3ADF-6344-8B10-3C6FE890D909}"/>
-    <hyperlink ref="A16" r:id="rId10" display="https://leetcode.cn/problems/web-crawler/solution/by-wywy-m-tq5x/" xr:uid="{1096138D-EBE2-324D-A769-E0CF4843CC45}"/>
-    <hyperlink ref="A17" r:id="rId11" display="https://leetcode.cn/problems/populating-next-right-pointers-in-each-node-ii/solution/117-by-wywy-m-2dey/" xr:uid="{DB4092D2-CEB5-5F40-9A2F-A3D1F3E1FAD5}"/>
-    <hyperlink ref="A18" r:id="rId12" display="https://leetcode.cn/problems/evaluate-division/solution/by-wywy-m-fqcc/" xr:uid="{3BA99F54-D69C-BE40-BD52-19CC44580857}"/>
-    <hyperlink ref="A19" r:id="rId13" display="https://leetcode.cn/problems/walls-and-gates/solution/286-by-wywy-m-v89r/" xr:uid="{A1807D7E-F45A-BC4D-A674-450FE3CC3465}"/>
-    <hyperlink ref="A22" r:id="rId14" display="https://leetcode.cn/problems/shortest-distance-from-all-buildings/solution/317-by-wywy-m-31q4/" xr:uid="{7C3F06B2-F6CE-D941-A3E6-9CC13D48726B}"/>
-    <hyperlink ref="A20" r:id="rId15" display="https://leetcode.cn/problems/01-matrix/solution/-by-wywy-m-1ak4/" xr:uid="{AC1F76FF-A2DA-694F-A769-2136BC16C971}"/>
-    <hyperlink ref="A24" r:id="rId16" display="https://leetcode.cn/problems/sliding-puzzle/solution/773-hua-dong-mi-ti-bfs-by-ywrx-c74s/" xr:uid="{0AD32694-5038-3D45-918C-C400FC7946DE}"/>
-    <hyperlink ref="A21" r:id="rId17" display="https://leetcode.cn/problems/open-the-lock/solution/752-da-kai-zhuan-pan-suo-bfs-by-ywrx-y6lu/" xr:uid="{479482D9-B268-4348-9013-D7B5073218A6}"/>
-    <hyperlink ref="A40" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
-    <hyperlink ref="A41" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
-    <hyperlink ref="A32" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
-    <hyperlink ref="A33" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
-    <hyperlink ref="A34" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
-    <hyperlink ref="A35" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
-    <hyperlink ref="A36" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
-    <hyperlink ref="A37" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
-    <hyperlink ref="A38" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
-    <hyperlink ref="A39" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
-    <hyperlink ref="A42" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
-    <hyperlink ref="A43" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
-    <hyperlink ref="A23" r:id="rId29" xr:uid="{F7F1BE06-524D-3F45-A6A1-43D1A4059E77}"/>
+    <hyperlink ref="A14" r:id="rId8" display="https://leetcode-cn.com/problems/shortest-path-in-binary-matrix/solution/1091-er-jin-zhi-ju-zhen-zui-duan-lu-jing-00dr/" xr:uid="{678CC0D2-5BB2-9447-A9D9-85A1922DAD7A}"/>
+    <hyperlink ref="A16" r:id="rId9" display="https://leetcode.cn/problems/ji-qi-ren-de-yun-dong-fan-wei-lcof/solution/-by-wywy-m-hks2/" xr:uid="{433B27C5-3ADF-6344-8B10-3C6FE890D909}"/>
+    <hyperlink ref="A17" r:id="rId10" display="https://leetcode.cn/problems/web-crawler/solution/by-wywy-m-tq5x/" xr:uid="{1096138D-EBE2-324D-A769-E0CF4843CC45}"/>
+    <hyperlink ref="A18" r:id="rId11" display="https://leetcode.cn/problems/populating-next-right-pointers-in-each-node-ii/solution/117-by-wywy-m-2dey/" xr:uid="{DB4092D2-CEB5-5F40-9A2F-A3D1F3E1FAD5}"/>
+    <hyperlink ref="A19" r:id="rId12" display="https://leetcode.cn/problems/evaluate-division/solution/by-wywy-m-fqcc/" xr:uid="{3BA99F54-D69C-BE40-BD52-19CC44580857}"/>
+    <hyperlink ref="A20" r:id="rId13" display="https://leetcode.cn/problems/walls-and-gates/solution/286-by-wywy-m-v89r/" xr:uid="{A1807D7E-F45A-BC4D-A674-450FE3CC3465}"/>
+    <hyperlink ref="A23" r:id="rId14" display="https://leetcode.cn/problems/shortest-distance-from-all-buildings/solution/317-by-wywy-m-31q4/" xr:uid="{7C3F06B2-F6CE-D941-A3E6-9CC13D48726B}"/>
+    <hyperlink ref="A21" r:id="rId15" display="https://leetcode.cn/problems/01-matrix/solution/-by-wywy-m-1ak4/" xr:uid="{AC1F76FF-A2DA-694F-A769-2136BC16C971}"/>
+    <hyperlink ref="A25" r:id="rId16" display="https://leetcode.cn/problems/sliding-puzzle/solution/773-hua-dong-mi-ti-bfs-by-ywrx-c74s/" xr:uid="{0AD32694-5038-3D45-918C-C400FC7946DE}"/>
+    <hyperlink ref="A22" r:id="rId17" display="https://leetcode.cn/problems/open-the-lock/solution/752-da-kai-zhuan-pan-suo-bfs-by-ywrx-y6lu/" xr:uid="{479482D9-B268-4348-9013-D7B5073218A6}"/>
+    <hyperlink ref="A41" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
+    <hyperlink ref="A42" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
+    <hyperlink ref="A33" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
+    <hyperlink ref="A34" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
+    <hyperlink ref="A35" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
+    <hyperlink ref="A36" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
+    <hyperlink ref="A37" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
+    <hyperlink ref="A38" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
+    <hyperlink ref="A39" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
+    <hyperlink ref="A40" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
+    <hyperlink ref="A43" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
+    <hyperlink ref="A44" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
+    <hyperlink ref="A24" r:id="rId29" xr:uid="{F7F1BE06-524D-3F45-A6A1-43D1A4059E77}"/>
     <hyperlink ref="A9" r:id="rId30" xr:uid="{0E22DCEF-0BC9-3444-97D4-2AB1C84A8351}"/>
     <hyperlink ref="A10" r:id="rId31" xr:uid="{287B3E6D-9056-694F-B287-0EF92D0296AA}"/>
-    <hyperlink ref="A44" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
-    <hyperlink ref="A25" r:id="rId33" xr:uid="{ED5D89E9-76CF-A048-BD72-F0BA151EEC9F}"/>
-    <hyperlink ref="A45" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
-    <hyperlink ref="A46" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
-    <hyperlink ref="A11" r:id="rId36" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
-    <hyperlink ref="A47" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
-    <hyperlink ref="A26" r:id="rId38" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
-    <hyperlink ref="A48" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
-    <hyperlink ref="A27" r:id="rId40" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
-    <hyperlink ref="A30" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
-    <hyperlink ref="A14" r:id="rId42" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
-    <hyperlink ref="A28" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
-    <hyperlink ref="A29" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
+    <hyperlink ref="A45" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
+    <hyperlink ref="A26" r:id="rId33" xr:uid="{ED5D89E9-76CF-A048-BD72-F0BA151EEC9F}"/>
+    <hyperlink ref="A46" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
+    <hyperlink ref="A47" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
+    <hyperlink ref="A12" r:id="rId36" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
+    <hyperlink ref="A48" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
+    <hyperlink ref="A27" r:id="rId38" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
+    <hyperlink ref="A49" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
+    <hyperlink ref="A28" r:id="rId40" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
+    <hyperlink ref="A31" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
+    <hyperlink ref="A15" r:id="rId42" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
+    <hyperlink ref="A29" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
+    <hyperlink ref="A30" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
+    <hyperlink ref="A11" r:id="rId45" xr:uid="{89528EDA-A621-6D4D-A2DD-9DE18BC8A31E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6562,7 +6598,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF43907A-09FF-DA4F-B1FC-56FBDF277DF3}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.33203125" style="6" customWidth="1"/>
@@ -6844,6 +6880,17 @@
       </c>
       <c r="C25" s="6">
         <v>20250207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="6">
+        <v>20250712</v>
       </c>
     </row>
   </sheetData>
@@ -6875,6 +6922,7 @@
     <hyperlink ref="A15" r:id="rId22" xr:uid="{6847C139-E778-DD49-8716-EA4DC6A4B249}"/>
     <hyperlink ref="A24" r:id="rId23" xr:uid="{14DAD402-D9AB-3B4C-9CF0-4AE842DC5CFC}"/>
     <hyperlink ref="A25" r:id="rId24" xr:uid="{CA519943-21A7-954B-B099-5F9DD0AFBE8B}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{D95F4FCB-87B2-B740-BDD9-741AAA1AC803}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7255,7 +7303,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C589BEE-21A2-4E43-9E3C-F419C25A1E80}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24.83203125" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.5" style="10" customWidth="1"/>
@@ -7329,6 +7377,17 @@
         <v>20230403</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10">
+        <v>20250712</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://leetcode-cn.com/problems/integer-to-english-words/solution/273-zheng-shu-zhuan-huan-ying-wen-biao-s-d9es/" xr:uid="{6A706088-D403-F94C-894B-198211511F89}"/>
@@ -7336,6 +7395,7 @@
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.cn/problems/shu-de-zi-jie-gou-lcof/solution/by-wywy-m-2zs3/" xr:uid="{9C6AD427-7F35-8A46-BE8D-8AE263AD5051}"/>
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/integer-to-english-words/solution/by-wywy-m-4yer/" xr:uid="{4208DCE0-2370-3C48-8A98-BD04CF3C5890}"/>
     <hyperlink ref="A6" r:id="rId5" xr:uid="{D2B24540-D3F4-BB42-AE97-BDB45B74E404}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{3DCD20F0-4E25-584B-B97C-5A305AC259D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7933,17 +7993,6 @@
       </c>
       <c r="C46" s="10">
         <v>20230402</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C47" s="10">
-        <v>20230623</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -8069,16 +8118,15 @@
     <hyperlink ref="A45" r:id="rId28" xr:uid="{3524C6A1-4A90-054F-AC10-D37588A6DB15}"/>
     <hyperlink ref="A46" r:id="rId29" xr:uid="{C4AE7CA4-776B-F248-BA2A-4D5B88729A2A}"/>
     <hyperlink ref="A39" r:id="rId30" xr:uid="{00C655BE-BF34-394D-B73C-277004BB9169}"/>
-    <hyperlink ref="A47" r:id="rId31" xr:uid="{04785873-4BDF-2C4F-9B49-0979DE807FBD}"/>
-    <hyperlink ref="A48" r:id="rId32" xr:uid="{84DF03EA-CC86-A04A-8296-9AEC9DFD2E60}"/>
-    <hyperlink ref="A49" r:id="rId33" xr:uid="{A3C11DAC-3BD4-2B45-AF12-06D1D1F3C454}"/>
-    <hyperlink ref="A50" r:id="rId34" xr:uid="{8C8663BB-59DF-1442-88D7-61A61DD13696}"/>
-    <hyperlink ref="A51" r:id="rId35" xr:uid="{AF4F0AAA-D927-004F-BF47-594C7E828832}"/>
-    <hyperlink ref="A52" r:id="rId36" xr:uid="{B70D3013-9C89-9D44-801C-76A4CBC9C633}"/>
-    <hyperlink ref="A53" r:id="rId37" xr:uid="{6CCC68C6-FBF8-0641-A35A-D2F41894650E}"/>
-    <hyperlink ref="A54" r:id="rId38" xr:uid="{23504A27-82D3-7141-94CB-F17A82D6A7EF}"/>
-    <hyperlink ref="A55" r:id="rId39" xr:uid="{8B2B0486-5360-9745-A744-589A7CCFC882}"/>
-    <hyperlink ref="A13" r:id="rId40" xr:uid="{DB5E8E4D-CC40-9D47-951E-0B84D4FB4309}"/>
+    <hyperlink ref="A48" r:id="rId31" xr:uid="{84DF03EA-CC86-A04A-8296-9AEC9DFD2E60}"/>
+    <hyperlink ref="A49" r:id="rId32" xr:uid="{A3C11DAC-3BD4-2B45-AF12-06D1D1F3C454}"/>
+    <hyperlink ref="A50" r:id="rId33" xr:uid="{8C8663BB-59DF-1442-88D7-61A61DD13696}"/>
+    <hyperlink ref="A51" r:id="rId34" xr:uid="{AF4F0AAA-D927-004F-BF47-594C7E828832}"/>
+    <hyperlink ref="A52" r:id="rId35" xr:uid="{B70D3013-9C89-9D44-801C-76A4CBC9C633}"/>
+    <hyperlink ref="A53" r:id="rId36" xr:uid="{6CCC68C6-FBF8-0641-A35A-D2F41894650E}"/>
+    <hyperlink ref="A54" r:id="rId37" xr:uid="{23504A27-82D3-7141-94CB-F17A82D6A7EF}"/>
+    <hyperlink ref="A55" r:id="rId38" xr:uid="{8B2B0486-5360-9745-A744-589A7CCFC882}"/>
+    <hyperlink ref="A13" r:id="rId39" xr:uid="{DB5E8E4D-CC40-9D47-951E-0B84D4FB4309}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8374,7 +8422,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C38DCB7-D208-4A47-A52C-374E9CD57FFC}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="75.33203125" style="10" customWidth="1"/>
@@ -8810,6 +8858,17 @@
       </c>
       <c r="C39" s="10">
         <v>20250203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="10">
+        <v>20250713</v>
       </c>
     </row>
   </sheetData>
@@ -8851,6 +8910,7 @@
     <hyperlink ref="A37" r:id="rId32" xr:uid="{AFEE2B65-0EB5-8846-96DB-567E9DE4E31F}"/>
     <hyperlink ref="A38" r:id="rId33" xr:uid="{0B9688B0-16FD-DB40-81CA-08F04015EC9E}"/>
     <hyperlink ref="A39" r:id="rId34" xr:uid="{D9396FEF-5806-3A40-B6A0-D564AAC78028}"/>
+    <hyperlink ref="A40" r:id="rId35" xr:uid="{04785873-4BDF-2C4F-9B49-0979DE807FBD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9528,7 +9588,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="7">
-        <v>20230110</v>
+        <v>20250713</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E8D2C6-F459-6B48-A8F2-09B7EC0A0956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F37EC7-1621-C24B-AC07-35627B33C46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" activeTab="8" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" firstSheet="5" activeTab="15" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="505">
   <si>
     <t>#</t>
   </si>
@@ -1557,6 +1557,18 @@
   </si>
   <si>
     <t>277 搜寻名人</t>
+  </si>
+  <si>
+    <t>Eulerian Path</t>
+  </si>
+  <si>
+    <t>332 重新安排行程</t>
+  </si>
+  <si>
+    <t>410 分割数组的最大值</t>
+  </si>
+  <si>
+    <t>465 最优账单平衡</t>
   </si>
 </sst>
 </file>
@@ -2858,7 +2870,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF52CBDF-A54F-B64B-ABC7-BC9DA66EFACF}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" style="10" customWidth="1"/>
@@ -3613,6 +3625,17 @@
       </c>
       <c r="C68" s="10">
         <v>20250713</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" s="10">
+        <v>20250717</v>
       </c>
     </row>
   </sheetData>
@@ -3677,6 +3700,7 @@
     <hyperlink ref="A67" r:id="rId55" xr:uid="{A77FFA44-1F03-2D4A-AD88-E7428C9AA2D5}"/>
     <hyperlink ref="A8" r:id="rId56" display="https://leetcode.cn/problems/unique-paths/solutions/3057839/62-bu-tong-lu-jing-dp-by-ywrx-rh78/" xr:uid="{46A1A02C-4549-4046-98BB-52A767D35641}"/>
     <hyperlink ref="A68" r:id="rId57" xr:uid="{E80A8A71-063F-A44D-8B00-EB348F17438D}"/>
+    <hyperlink ref="A69" r:id="rId58" xr:uid="{4712E19F-E9AB-EB41-88EA-1E0F711FE97E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4568,7 +4592,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3390D82-F280-2841-A652-0961C2865E3C}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.1640625" style="10" customWidth="1"/>
@@ -5119,6 +5143,25 @@
       <c r="C50" s="7">
         <v>20250114</v>
       </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="10">
+        <v>20250717</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:C25">
@@ -5171,6 +5214,7 @@
     <hyperlink ref="A29" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
     <hyperlink ref="A30" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
     <hyperlink ref="A11" r:id="rId45" xr:uid="{89528EDA-A621-6D4D-A2DD-9DE18BC8A31E}"/>
+    <hyperlink ref="A52" r:id="rId46" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5178,7 +5222,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F10A632-C78C-6347-8E5A-4720E264DA34}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="82" style="10" customWidth="1"/>
@@ -5493,6 +5537,17 @@
       </c>
       <c r="C28" s="10">
         <v>20250515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="10">
+        <v>20250718</v>
       </c>
     </row>
   </sheetData>
@@ -5527,6 +5582,7 @@
     <hyperlink ref="A26" r:id="rId25" xr:uid="{52643BBF-D205-AC4A-B6DD-A848E889D1C5}"/>
     <hyperlink ref="A27" r:id="rId26" xr:uid="{58B4B8F6-E0EF-5346-882E-AC144A6A8A6D}"/>
     <hyperlink ref="A28" r:id="rId27" xr:uid="{020F6F1B-4062-1847-A3F0-2861731DC376}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{DF19D5B2-DD91-FE43-9464-1009CFE3AF36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F37EC7-1621-C24B-AC07-35627B33C46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91659DE-8D9D-0442-AE1D-05BE3E4C941A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" firstSheet="5" activeTab="15" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" activeTab="12" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="521">
   <si>
     <t>#</t>
   </si>
@@ -1569,6 +1569,54 @@
   </si>
   <si>
     <t>465 最优账单平衡</t>
+  </si>
+  <si>
+    <t>490 迷宫</t>
+  </si>
+  <si>
+    <t>540 有序数组中的单一元素</t>
+  </si>
+  <si>
+    <t>632 最小区间</t>
+  </si>
+  <si>
+    <t>642 设计搜索自动补全系统</t>
+  </si>
+  <si>
+    <t>720 词典中最长的单词</t>
+  </si>
+  <si>
+    <t>767 重构字符串</t>
+  </si>
+  <si>
+    <t>785 判断二分图</t>
+  </si>
+  <si>
+    <t>886 可能的二分法</t>
+  </si>
+  <si>
+    <t>2232 向表达式添加括号后的最小结果</t>
+  </si>
+  <si>
+    <t>1996 游戏中弱角色的数量</t>
+  </si>
+  <si>
+    <t>1235 规划兼职工作</t>
+  </si>
+  <si>
+    <t>2402 会议室III</t>
+  </si>
+  <si>
+    <t>980 不同路径III</t>
+  </si>
+  <si>
+    <t>1306 跳跃游戏III</t>
+  </si>
+  <si>
+    <t>759 员工空闲时间</t>
+  </si>
+  <si>
+    <t>CN没有更新</t>
   </si>
 </sst>
 </file>
@@ -2536,14 +2584,14 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>540</v>
+      <c r="A7" s="8" t="s">
+        <v>506</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>4</v>
+      <c r="C7" s="7">
+        <v>20250719</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2754,6 +2802,7 @@
     <hyperlink ref="A24" r:id="rId14" xr:uid="{B197C4EF-BBFA-9C4D-8935-1591C8CD319E}"/>
     <hyperlink ref="A10" r:id="rId15" xr:uid="{9C812532-9B74-F245-9727-E6278385A520}"/>
     <hyperlink ref="A11" r:id="rId16" xr:uid="{B75B3B15-223A-154E-B443-CA5C70F537A6}"/>
+    <hyperlink ref="A7" r:id="rId17" xr:uid="{7BC51ED3-D8F0-4E4C-AE63-756A29B376C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2870,7 +2919,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF52CBDF-A54F-B64B-ABC7-BC9DA66EFACF}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" style="10" customWidth="1"/>
@@ -3636,6 +3685,17 @@
       </c>
       <c r="C69" s="10">
         <v>20250717</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="10">
+        <v>20250720</v>
       </c>
     </row>
   </sheetData>
@@ -3701,6 +3761,7 @@
     <hyperlink ref="A8" r:id="rId56" display="https://leetcode.cn/problems/unique-paths/solutions/3057839/62-bu-tong-lu-jing-dp-by-ywrx-rh78/" xr:uid="{46A1A02C-4549-4046-98BB-52A767D35641}"/>
     <hyperlink ref="A68" r:id="rId57" xr:uid="{E80A8A71-063F-A44D-8B00-EB348F17438D}"/>
     <hyperlink ref="A69" r:id="rId58" xr:uid="{4712E19F-E9AB-EB41-88EA-1E0F711FE97E}"/>
+    <hyperlink ref="A70" r:id="rId59" xr:uid="{5A9FFCE5-A402-3347-BE28-0BA8C267259D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3708,13 +3769,14 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E45454-ABB5-A740-839B-4BC8D58C720C}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.6640625" style="10" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="10"/>
     <col min="3" max="3" width="22.83203125" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="10"/>
+    <col min="4" max="4" width="25.33203125" style="10" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -4069,7 +4131,7 @@
         <v>20230322</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>343</v>
       </c>
@@ -4080,7 +4142,7 @@
         <v>20230323</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>355</v>
       </c>
@@ -4091,7 +4153,7 @@
         <v>20230327</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>21</v>
       </c>
@@ -4102,7 +4164,7 @@
         <v>20230404</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>394</v>
       </c>
@@ -4113,7 +4175,7 @@
         <v>20230427</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>409</v>
       </c>
@@ -4124,7 +4186,7 @@
         <v>20230507</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>433</v>
       </c>
@@ -4135,7 +4197,7 @@
         <v>20240510</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>463</v>
       </c>
@@ -4144,6 +4206,42 @@
       </c>
       <c r="C39" s="10">
         <v>20250122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="10">
+        <v>20250720</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="10">
+        <v>20250720</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="10">
+        <v>20250722</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -4181,6 +4279,9 @@
     <hyperlink ref="A37" r:id="rId28" xr:uid="{65AC0A5C-BD2D-BC4B-B3E5-8FC3E2DC8587}"/>
     <hyperlink ref="A38" r:id="rId29" xr:uid="{1EB3DF06-331C-0A4D-B8EC-6D9F02E81459}"/>
     <hyperlink ref="A39" r:id="rId30" xr:uid="{222DF16D-09EE-0846-B95C-1D47077C9925}"/>
+    <hyperlink ref="A40" r:id="rId31" xr:uid="{CE7625CA-251C-124F-B0CB-2ED6EC2CCA31}"/>
+    <hyperlink ref="A41" r:id="rId32" xr:uid="{4A2C7437-1B73-5845-9C64-255209AFF8FB}"/>
+    <hyperlink ref="A42" r:id="rId33" xr:uid="{B190EF91-A632-8B46-825F-8B6041E51FB4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4592,7 +4693,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3390D82-F280-2841-A652-0961C2865E3C}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.1640625" style="10" customWidth="1"/>
@@ -4940,79 +5041,79 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="7">
+        <v>20250719</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="7">
+        <v>20250720</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="7">
+        <v>20250720</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="7">
+      <c r="B36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="7">
         <v>20220925</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="7">
+      <c r="B37" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="7">
         <v>20250506</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="7">
+      <c r="B38" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="7">
         <v>20220906</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="7">
-        <v>20220906</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="7">
-        <v>20220906</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="7">
-        <v>20250126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>243</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>5</v>
@@ -5021,9 +5122,9 @@
         <v>20220906</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>5</v>
@@ -5032,136 +5133,169 @@
         <v>20220906</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="7">
+        <v>20250126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="7">
+        <v>20220906</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="7">
+        <v>20220906</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="7">
+      <c r="B44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="7">
         <v>20220913</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="7">
+      <c r="B45" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="7">
         <v>20220923</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="7">
+      <c r="B46" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="7">
         <v>20230308</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="7">
+      <c r="B47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="7">
         <v>20230319</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="7">
+      <c r="B48" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="7">
         <v>20230415</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="7">
+      <c r="B49" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="7">
         <v>20230429</v>
       </c>
-      <c r="E46" s="8"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="10">
+      <c r="B50" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="10">
         <v>20230623</v>
       </c>
-      <c r="E47" s="14"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
+      <c r="E50" s="14"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="10">
+      <c r="B51" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="10">
         <v>20240504</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="10">
+      <c r="B52" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="10">
         <v>20240512</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="7">
+      <c r="B53" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="7">
         <v>20250114</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="10">
+      <c r="B55" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="10">
         <v>20250717</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:C25">
@@ -5169,7 +5303,7 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="https://leetcode.cn/problems/all-paths-from-source-to-target/solution/by-wywy-m-nqp0/" xr:uid="{62AA1BDA-9AEF-1D4E-985F-E4BFC300F9ED}"/>
-    <hyperlink ref="A50" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
+    <hyperlink ref="A53" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.cn/problems/path-with-minimum-effort/solution/1631-zui-xiao-ti-li-xiao-hao-lu-jing-dij-36ok/" xr:uid="{B4E6A033-CD2E-1C4F-A02F-38038DA461CB}"/>
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/path-with-maximum-probability/solution/1514-gai-lu-zui-da-de-lu-jing-dijkstra-b-kh0n/" xr:uid="{8F9369A4-3430-114E-8817-0069A16021C5}"/>
     <hyperlink ref="A6" r:id="rId5" display="https://leetcode.cn/problems/course-schedule-ii/solution/210-ke-cheng-biao-iigraph-by-wywy-m-18nk/" xr:uid="{C7EEFC8F-2387-F14A-B36C-A22ACD69ECCB}"/>
@@ -5185,44 +5319,48 @@
     <hyperlink ref="A21" r:id="rId15" display="https://leetcode.cn/problems/01-matrix/solution/-by-wywy-m-1ak4/" xr:uid="{AC1F76FF-A2DA-694F-A769-2136BC16C971}"/>
     <hyperlink ref="A25" r:id="rId16" display="https://leetcode.cn/problems/sliding-puzzle/solution/773-hua-dong-mi-ti-bfs-by-ywrx-c74s/" xr:uid="{0AD32694-5038-3D45-918C-C400FC7946DE}"/>
     <hyperlink ref="A22" r:id="rId17" display="https://leetcode.cn/problems/open-the-lock/solution/752-da-kai-zhuan-pan-suo-bfs-by-ywrx-y6lu/" xr:uid="{479482D9-B268-4348-9013-D7B5073218A6}"/>
-    <hyperlink ref="A41" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
-    <hyperlink ref="A42" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
-    <hyperlink ref="A33" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
-    <hyperlink ref="A34" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
-    <hyperlink ref="A35" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
-    <hyperlink ref="A36" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
-    <hyperlink ref="A37" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
-    <hyperlink ref="A38" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
-    <hyperlink ref="A39" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
-    <hyperlink ref="A40" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
-    <hyperlink ref="A43" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
-    <hyperlink ref="A44" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
+    <hyperlink ref="A44" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
+    <hyperlink ref="A45" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
+    <hyperlink ref="A36" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
+    <hyperlink ref="A37" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
+    <hyperlink ref="A38" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
+    <hyperlink ref="A39" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
+    <hyperlink ref="A40" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
+    <hyperlink ref="A41" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
+    <hyperlink ref="A42" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
+    <hyperlink ref="A43" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
+    <hyperlink ref="A46" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
+    <hyperlink ref="A47" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
     <hyperlink ref="A24" r:id="rId29" xr:uid="{F7F1BE06-524D-3F45-A6A1-43D1A4059E77}"/>
     <hyperlink ref="A9" r:id="rId30" xr:uid="{0E22DCEF-0BC9-3444-97D4-2AB1C84A8351}"/>
     <hyperlink ref="A10" r:id="rId31" xr:uid="{287B3E6D-9056-694F-B287-0EF92D0296AA}"/>
-    <hyperlink ref="A45" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
+    <hyperlink ref="A48" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
     <hyperlink ref="A26" r:id="rId33" xr:uid="{ED5D89E9-76CF-A048-BD72-F0BA151EEC9F}"/>
-    <hyperlink ref="A46" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
-    <hyperlink ref="A47" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
+    <hyperlink ref="A49" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
+    <hyperlink ref="A50" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
     <hyperlink ref="A12" r:id="rId36" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
-    <hyperlink ref="A48" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
+    <hyperlink ref="A51" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
     <hyperlink ref="A27" r:id="rId38" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
-    <hyperlink ref="A49" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
+    <hyperlink ref="A52" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
     <hyperlink ref="A28" r:id="rId40" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
     <hyperlink ref="A31" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
     <hyperlink ref="A15" r:id="rId42" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
     <hyperlink ref="A29" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
     <hyperlink ref="A30" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
     <hyperlink ref="A11" r:id="rId45" xr:uid="{89528EDA-A621-6D4D-A2DD-9DE18BC8A31E}"/>
-    <hyperlink ref="A52" r:id="rId46" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
+    <hyperlink ref="A55" r:id="rId46" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
+    <hyperlink ref="A32" r:id="rId47" xr:uid="{8AF59068-3701-144D-866B-DF434B216EEE}"/>
+    <hyperlink ref="A33" r:id="rId48" xr:uid="{CBACF588-0969-4A43-8A15-7D5C7F053B5C}"/>
+    <hyperlink ref="A34" r:id="rId49" xr:uid="{97AE6A05-E848-194F-99D0-CB202FE98A50}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F10A632-C78C-6347-8E5A-4720E264DA34}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="82" style="10" customWidth="1"/>
@@ -5382,7 +5520,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="7">
-        <v>20230218</v>
+        <v>20250719</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -5548,6 +5686,28 @@
       </c>
       <c r="C29" s="10">
         <v>20250718</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="10">
+        <v>20250720</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="10">
+        <v>20250722</v>
       </c>
     </row>
   </sheetData>
@@ -5569,7 +5729,7 @@
     <hyperlink ref="A12" r:id="rId12" display="https://leetcode.cn/problems/partition-to-k-equal-sum-subsets/solution/by-wywy-m-7u79/" xr:uid="{2A982970-7916-654D-8803-A4DF44697B6E}"/>
     <hyperlink ref="A20" r:id="rId13" display="https://leetcode.cn/problems/word-break-ii/solution/140-dan-ci-by-wywy-m-ehbg/" xr:uid="{782AF1CE-4F40-DA4F-A47B-B67F718B6316}"/>
     <hyperlink ref="A13" r:id="rId14" display="https://leetcode.cn/problems/path-sum-ii/solution/113-lu-jing-zong-he-ii-by-wywy-m-2w34/" xr:uid="{835783B1-390F-484E-894C-5491D48B50F2}"/>
-    <hyperlink ref="A14" r:id="rId15" display="https://leetcode.cn/problems/YaVDxD/solution/494-mu-biao-he-hui-su-by-wywy-m-4geb/" xr:uid="{F70A3037-F220-104C-8118-DFEF831779B3}"/>
+    <hyperlink ref="A14" r:id="rId15" xr:uid="{F70A3037-F220-104C-8118-DFEF831779B3}"/>
     <hyperlink ref="A15" r:id="rId16" display="https://leetcode.cn/problems/non-decreasing-subsequences/solution/491-di-zeng-zi-xu-lie-hui-su-by-wywy-m-sy6c/" xr:uid="{09BDB8A5-72EC-954C-9E70-AC0C9E3103E9}"/>
     <hyperlink ref="A21" r:id="rId17" display="https://leetcode.cn/problems/sudoku-solver/solution/37-jie-shu-du-hui-su-by-wywy-m-oqis/" xr:uid="{12822379-D53C-BB47-8A33-C2644AF9559A}"/>
     <hyperlink ref="A16" r:id="rId18" xr:uid="{D24AD4DE-7995-A644-8178-F78252CC042B}"/>
@@ -5583,6 +5743,8 @@
     <hyperlink ref="A27" r:id="rId26" xr:uid="{58B4B8F6-E0EF-5346-882E-AC144A6A8A6D}"/>
     <hyperlink ref="A28" r:id="rId27" xr:uid="{020F6F1B-4062-1847-A3F0-2861731DC376}"/>
     <hyperlink ref="A29" r:id="rId28" xr:uid="{DF19D5B2-DD91-FE43-9464-1009CFE3AF36}"/>
+    <hyperlink ref="A30" r:id="rId29" display="1306 跳跃游戏" xr:uid="{B4339213-63EF-E54E-87E9-20B533BF7F44}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{B7B72A55-6E11-C344-86D7-730B25BA5254}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6654,7 +6816,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF43907A-09FF-DA4F-B1FC-56FBDF277DF3}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.33203125" style="6" customWidth="1"/>
@@ -6947,6 +7109,17 @@
       </c>
       <c r="C26" s="6">
         <v>20250712</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="6">
+        <v>20250720</v>
       </c>
     </row>
   </sheetData>
@@ -6979,6 +7152,7 @@
     <hyperlink ref="A24" r:id="rId23" xr:uid="{14DAD402-D9AB-3B4C-9CF0-4AE842DC5CFC}"/>
     <hyperlink ref="A25" r:id="rId24" xr:uid="{CA519943-21A7-954B-B099-5F9DD0AFBE8B}"/>
     <hyperlink ref="A26" r:id="rId25" xr:uid="{D95F4FCB-87B2-B740-BDD9-741AAA1AC803}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{A6CFCEA1-4FD3-254E-8C7E-D0AE4396B517}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8478,7 +8652,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C38DCB7-D208-4A47-A52C-374E9CD57FFC}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="75.33203125" style="10" customWidth="1"/>
@@ -8925,6 +9099,28 @@
       </c>
       <c r="C40" s="10">
         <v>20250713</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="10">
+        <v>20250719</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="10">
+        <v>20250719</v>
       </c>
     </row>
   </sheetData>
@@ -8967,6 +9163,8 @@
     <hyperlink ref="A38" r:id="rId33" xr:uid="{0B9688B0-16FD-DB40-81CA-08F04015EC9E}"/>
     <hyperlink ref="A39" r:id="rId34" xr:uid="{D9396FEF-5806-3A40-B6A0-D564AAC78028}"/>
     <hyperlink ref="A40" r:id="rId35" xr:uid="{04785873-4BDF-2C4F-9B49-0979DE807FBD}"/>
+    <hyperlink ref="A41" r:id="rId36" xr:uid="{39C352BC-02CC-B64F-BBA4-2D978CE750A4}"/>
+    <hyperlink ref="A42" r:id="rId37" xr:uid="{8F285B38-2D86-BA45-8427-9B3EFAAC58E0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9572,7 +9770,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAA87E2-0C96-3045-BD9E-C5C85205F434}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.33203125" style="6" customWidth="1"/>
@@ -9699,7 +9897,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>20230620</v>
+        <v>20250721</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -9755,6 +9953,28 @@
       </c>
       <c r="C16" s="6">
         <v>20250629</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>20250719</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>20250721</v>
       </c>
     </row>
   </sheetData>
@@ -9777,6 +9997,8 @@
     <hyperlink ref="A14" r:id="rId13" xr:uid="{8B97E3E3-F60B-A64D-BFFC-2C4D92E1EACE}"/>
     <hyperlink ref="A15" r:id="rId14" xr:uid="{3D86F3EA-BD46-4F47-93AA-0882C9D9D61F}"/>
     <hyperlink ref="A16" r:id="rId15" xr:uid="{CBFBF69D-7CE2-0943-91D7-4BB1286A5EDC}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{331EC6DD-E2C5-6E47-BBAD-0BBA050507AA}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{78274215-8135-934A-A277-E6C94E09DFE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91659DE-8D9D-0442-AE1D-05BE3E4C941A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781148C2-D095-3941-9D83-8D033B88FC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" activeTab="12" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28040" windowHeight="15920" activeTab="1" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="522">
   <si>
     <t>#</t>
   </si>
@@ -1617,6 +1617,9 @@
   </si>
   <si>
     <t>CN没有更新</t>
+  </si>
+  <si>
+    <t>7 整数反转</t>
   </si>
 </sst>
 </file>
@@ -6816,7 +6819,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF43907A-09FF-DA4F-B1FC-56FBDF277DF3}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.33203125" style="6" customWidth="1"/>
@@ -7120,6 +7123,17 @@
       </c>
       <c r="C27" s="6">
         <v>20250720</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="6">
+        <v>20250802</v>
       </c>
     </row>
   </sheetData>
@@ -7153,6 +7167,7 @@
     <hyperlink ref="A25" r:id="rId24" xr:uid="{CA519943-21A7-954B-B099-5F9DD0AFBE8B}"/>
     <hyperlink ref="A26" r:id="rId25" xr:uid="{D95F4FCB-87B2-B740-BDD9-741AAA1AC803}"/>
     <hyperlink ref="A27" r:id="rId26" xr:uid="{A6CFCEA1-4FD3-254E-8C7E-D0AE4396B517}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{9EDE2E00-A8D2-424A-9CE5-970C33783CD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -9776,7 +9791,9 @@
     <col min="1" max="1" width="52.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="6"/>
     <col min="3" max="3" width="14.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="6"/>
+    <col min="4" max="4" width="11.1640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.3">

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10107"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781148C2-D095-3941-9D83-8D033B88FC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2908EE7-685C-0640-9F3B-499E16B74F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28040" windowHeight="15920" activeTab="1" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28760" windowHeight="17280" firstSheet="5" activeTab="18" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="524">
   <si>
     <t>#</t>
   </si>
@@ -1620,6 +1620,12 @@
   </si>
   <si>
     <t>7 整数反转</t>
+  </si>
+  <si>
+    <t xml:space="preserve">432 全O(1)的数据结构 </t>
+  </si>
+  <si>
+    <t>364 嵌套列表加权和II</t>
   </si>
 </sst>
 </file>
@@ -4696,7 +4702,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3390D82-F280-2841-A652-0961C2865E3C}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.1640625" style="10" customWidth="1"/>
@@ -5077,46 +5083,46 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="7">
+        <v>20250823</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="7">
-        <v>20220925</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="7">
-        <v>20250506</v>
+        <v>20220925</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="7">
-        <v>20220906</v>
+        <v>20250506</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>5</v>
@@ -5127,7 +5133,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>5</v>
@@ -5138,29 +5144,29 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="7">
-        <v>20250126</v>
+        <v>20220906</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="7">
-        <v>20220906</v>
+        <v>20250126</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>5</v>
@@ -5171,134 +5177,145 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C44" s="7">
-        <v>20220913</v>
+        <v>20220906</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="7">
-        <v>20220923</v>
+        <v>20220913</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="7">
-        <v>20230308</v>
+        <v>20220923</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="7">
-        <v>20230319</v>
+        <v>20230308</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="7">
-        <v>20230415</v>
+        <v>20230319</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C49" s="7">
-        <v>20230429</v>
-      </c>
-      <c r="E49" s="8"/>
+        <v>20230415</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="10">
-        <v>20230623</v>
-      </c>
-      <c r="E50" s="14"/>
+        <v>398</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="7">
+        <v>20230429</v>
+      </c>
+      <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="10">
-        <v>20240504</v>
-      </c>
+        <v>20230623</v>
+      </c>
+      <c r="E51" s="14"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C52" s="10">
-        <v>20240512</v>
+        <v>20240504</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="10">
+        <v>20240512</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="7">
+      <c r="B54" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="7">
         <v>20250114</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="10">
+      <c r="B56" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="10">
         <v>20250717</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:C25">
@@ -5306,7 +5323,7 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="https://leetcode.cn/problems/all-paths-from-source-to-target/solution/by-wywy-m-nqp0/" xr:uid="{62AA1BDA-9AEF-1D4E-985F-E4BFC300F9ED}"/>
-    <hyperlink ref="A53" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
+    <hyperlink ref="A54" r:id="rId2" display="https://leetcode.cn/problems/course-schedule/solution/207-by-wywy-m-iecv/" xr:uid="{4586CA20-A066-9C41-B617-39E14AD51DA2}"/>
     <hyperlink ref="A4" r:id="rId3" display="https://leetcode.cn/problems/path-with-minimum-effort/solution/1631-zui-xiao-ti-li-xiao-hao-lu-jing-dij-36ok/" xr:uid="{B4E6A033-CD2E-1C4F-A02F-38038DA461CB}"/>
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/path-with-maximum-probability/solution/1514-gai-lu-zui-da-de-lu-jing-dijkstra-b-kh0n/" xr:uid="{8F9369A4-3430-114E-8817-0069A16021C5}"/>
     <hyperlink ref="A6" r:id="rId5" display="https://leetcode.cn/problems/course-schedule-ii/solution/210-ke-cheng-biao-iigraph-by-wywy-m-18nk/" xr:uid="{C7EEFC8F-2387-F14A-B36C-A22ACD69ECCB}"/>
@@ -5322,39 +5339,40 @@
     <hyperlink ref="A21" r:id="rId15" display="https://leetcode.cn/problems/01-matrix/solution/-by-wywy-m-1ak4/" xr:uid="{AC1F76FF-A2DA-694F-A769-2136BC16C971}"/>
     <hyperlink ref="A25" r:id="rId16" display="https://leetcode.cn/problems/sliding-puzzle/solution/773-hua-dong-mi-ti-bfs-by-ywrx-c74s/" xr:uid="{0AD32694-5038-3D45-918C-C400FC7946DE}"/>
     <hyperlink ref="A22" r:id="rId17" display="https://leetcode.cn/problems/open-the-lock/solution/752-da-kai-zhuan-pan-suo-bfs-by-ywrx-y6lu/" xr:uid="{479482D9-B268-4348-9013-D7B5073218A6}"/>
-    <hyperlink ref="A44" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
-    <hyperlink ref="A45" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
-    <hyperlink ref="A36" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
-    <hyperlink ref="A37" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
-    <hyperlink ref="A38" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
-    <hyperlink ref="A39" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
-    <hyperlink ref="A40" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
-    <hyperlink ref="A41" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
-    <hyperlink ref="A42" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
-    <hyperlink ref="A43" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
-    <hyperlink ref="A46" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
-    <hyperlink ref="A47" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
+    <hyperlink ref="A45" r:id="rId18" display="https://leetcode.cn/problems/serialize-and-deserialize-n-ary-tree/solution/-by-wywy-m-3tc6/" xr:uid="{8BE83A5B-40AC-A543-935A-56732443F452}"/>
+    <hyperlink ref="A46" display="329 矩阵中的最长递增路径" xr:uid="{328B0723-66CE-B245-91ED-6BD40D9C8C2D}"/>
+    <hyperlink ref="A37" r:id="rId19" display="https://leetcode.cn/problems/lexicographical-numbers/solution/by-wywy-m-zkeq/" xr:uid="{28DEC326-6FFF-FE45-9D81-FA88F9380338}"/>
+    <hyperlink ref="A38" r:id="rId20" display="https://leetcode.cn/problems/surrounded-regions/solution/130-bei-wei-rao-de-qu-yu-dfs-by-ywrx-mgaq/" xr:uid="{8185D2DF-B947-7249-A9B8-CB74F896DE51}"/>
+    <hyperlink ref="A39" r:id="rId21" display="https://leetcode.cn/problems/number-of-islands/solution/200-dao-yu-shu-liang-by-wywy-m-cxtr/" xr:uid="{FF9132AC-9049-064B-B540-E8D27BD1C30B}"/>
+    <hyperlink ref="A40" r:id="rId22" display="https://leetcode.cn/problems/number-of-closed-islands/solution/1254-tong-ji-feng-bi-by-wywy-m-qc5d/" xr:uid="{7F2AB7CB-072B-9448-BB8B-4B7470CEC5CE}"/>
+    <hyperlink ref="A41" r:id="rId23" display="https://leetcode.cn/problems/number-of-enclaves/solution/1020-fei-di-by-wywy-m-n8fe/" xr:uid="{BACB5764-3CC5-A84C-8DC0-4FD405B3E874}"/>
+    <hyperlink ref="A42" r:id="rId24" display="https://leetcode.cn/problems/max-area-of-island/solution/695-by-wywy-m-iuv4/" xr:uid="{17FBEAD3-6BD2-B54B-AFE1-BCD179AE4565}"/>
+    <hyperlink ref="A43" r:id="rId25" display="https://leetcode.cn/problems/count-sub-islands/solution/1905-tong-ji-zi-dao-yu-by-wywy-m-txx9/" xr:uid="{93A063DA-39C1-0549-B8E6-6D257572601D}"/>
+    <hyperlink ref="A44" r:id="rId26" display="https://leetcode.cn/problems/number-of-distinct-islands/solution/-by-wywy-m-mnp1/" xr:uid="{466941BD-CCDE-314E-A33B-DDE50A357DDB}"/>
+    <hyperlink ref="A47" r:id="rId27" display="https://leetcode.cn/problems/cracking-the-safe/solution/753-po-jie-bao-xian-xiang-tu-by-ywrx-sp9h/" xr:uid="{E7988CED-D4A4-354A-8874-C47FC910E55A}"/>
+    <hyperlink ref="A48" r:id="rId28" xr:uid="{BC741E33-D794-4148-9FE5-2D8C789A48D5}"/>
     <hyperlink ref="A24" r:id="rId29" xr:uid="{F7F1BE06-524D-3F45-A6A1-43D1A4059E77}"/>
     <hyperlink ref="A9" r:id="rId30" xr:uid="{0E22DCEF-0BC9-3444-97D4-2AB1C84A8351}"/>
     <hyperlink ref="A10" r:id="rId31" xr:uid="{287B3E6D-9056-694F-B287-0EF92D0296AA}"/>
-    <hyperlink ref="A48" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
+    <hyperlink ref="A49" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
     <hyperlink ref="A26" r:id="rId33" xr:uid="{ED5D89E9-76CF-A048-BD72-F0BA151EEC9F}"/>
-    <hyperlink ref="A49" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
-    <hyperlink ref="A50" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
+    <hyperlink ref="A50" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
+    <hyperlink ref="A51" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
     <hyperlink ref="A12" r:id="rId36" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
-    <hyperlink ref="A51" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
+    <hyperlink ref="A52" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
     <hyperlink ref="A27" r:id="rId38" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
-    <hyperlink ref="A52" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
+    <hyperlink ref="A53" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
     <hyperlink ref="A28" r:id="rId40" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
     <hyperlink ref="A31" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
     <hyperlink ref="A15" r:id="rId42" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
     <hyperlink ref="A29" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
     <hyperlink ref="A30" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
     <hyperlink ref="A11" r:id="rId45" xr:uid="{89528EDA-A621-6D4D-A2DD-9DE18BC8A31E}"/>
-    <hyperlink ref="A55" r:id="rId46" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
+    <hyperlink ref="A56" r:id="rId46" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
     <hyperlink ref="A32" r:id="rId47" xr:uid="{8AF59068-3701-144D-866B-DF434B216EEE}"/>
     <hyperlink ref="A33" r:id="rId48" xr:uid="{CBACF588-0969-4A43-8A15-7D5C7F053B5C}"/>
     <hyperlink ref="A34" r:id="rId49" xr:uid="{97AE6A05-E848-194F-99D0-CB202FE98A50}"/>
+    <hyperlink ref="A35" r:id="rId50" xr:uid="{25A08FC5-3ECE-2242-BBE5-070B267F3C14}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6370,10 +6388,10 @@
         <v>438</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" s="7">
-        <v>20240512</v>
+        <v>20250823</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -6496,19 +6514,19 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>155</v>
+      <c r="A7" s="10">
+        <v>739</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="10">
-        <v>20220919</v>
+      <c r="C7" s="10" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
-        <v>739</v>
+        <v>503</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>5</v>
@@ -6518,118 +6536,118 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>503</v>
+      <c r="A9" s="8" t="s">
+        <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>4</v>
+      <c r="C9" s="10">
+        <v>20220918</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="10">
-        <v>20220918</v>
+        <v>20221223</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="10">
-        <v>20221223</v>
+        <v>20220825</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="10">
-        <v>20220825</v>
+        <v>20220911</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="10">
-        <v>20220911</v>
+        <v>20220913</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="10">
-        <v>20220913</v>
+        <v>20250502</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="10">
-        <v>20250502</v>
+        <v>20250220</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="10">
-        <v>20250220</v>
+        <v>20221213</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>19</v>
+        <v>478</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="10">
-        <v>20221213</v>
+        <v>20250221</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>478</v>
+        <v>20</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="10">
-        <v>20250221</v>
+        <v>20230103</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>5</v>
@@ -6640,178 +6658,178 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="10">
-        <v>20230103</v>
+        <v>20230109</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="10">
-        <v>20230109</v>
+        <v>20230308</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C22" s="10">
-        <v>20230308</v>
+        <v>20220820</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="10">
-        <v>20220820</v>
+        <v>20250221</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="10">
-        <v>20250221</v>
+        <v>20220923</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="10">
-        <v>20220923</v>
+        <v>20221018</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>18</v>
+        <v>373</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C26" s="10">
-        <v>20221018</v>
+        <v>20230404</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" s="10">
-        <v>20230404</v>
+        <v>20230412</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C28" s="10">
-        <v>20230412</v>
+        <v>20240506</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>375</v>
+        <v>436</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C29" s="10">
-        <v>20240506</v>
+        <v>20240511</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C30" s="10">
-        <v>20240511</v>
+        <v>20250113</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" s="10">
-        <v>20250113</v>
+        <v>20250220</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="10">
-        <v>20250220</v>
+        <v>309</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="7">
+        <v>20250823</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C28">
-    <sortCondition ref="B2:B28" customList="E,M,H"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C27">
+    <sortCondition ref="B2:B27" customList="E,M,H"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" display="https://leetcode.cn/problems/min-stack/solution/by-wywy-m-pmwn/" xr:uid="{4DAFC561-706D-9C40-BBAB-26B4DA2D330C}"/>
-    <hyperlink ref="A10" r:id="rId2" display="https://leetcode.cn/problems/minimum-remove-to-make-valid-parentheses/solution/by-wywy-m-2t35/" xr:uid="{2EB1CF24-787A-924C-91DB-549CF776B0A3}"/>
-    <hyperlink ref="A11" r:id="rId3" display="https://leetcode.cn/problems/decode-string/solution/-by-wywy-m-lwwt/" xr:uid="{5D178BBF-6035-EF43-BDB9-401CBA123DDE}"/>
-    <hyperlink ref="A23" r:id="rId4" display="https://leetcode.cn/problems/minimize-deviation-in-array/solution/by-wywy-m-d6vv/" xr:uid="{E2C0663E-46FC-F44F-A9DE-3B2A01CCE254}"/>
-    <hyperlink ref="A5" r:id="rId5" display="https://leetcode.cn/problems/next-greater-element-i/solution/-by-wywy-m-kp32/" xr:uid="{1635017B-5E04-0C45-A816-7E5A4EC696E1}"/>
-    <hyperlink ref="A12" r:id="rId6" display="https://leetcode.cn/problems/daily-temperatures/solution/739-mei-ri-wen-du-dan-diao-zhan-by-wywy-p1tl2/" xr:uid="{3B9663B1-07C0-A449-A8A8-8B3DA416A5B6}"/>
-    <hyperlink ref="A13" r:id="rId7" display="https://leetcode.cn/problems/remove-all-adjacent-duplicates-in-string-ii/solution/-by-wywy-m-g883/" xr:uid="{87237311-64CB-414E-A007-E3D64354DEE2}"/>
-    <hyperlink ref="A14" r:id="rId8" display="https://leetcode.cn/problems/add-two-numbers-ii/solution/by-wywy-m-kr74/" xr:uid="{E4C9551A-9B0F-3044-9E93-3D2801442FA6}"/>
-    <hyperlink ref="A15" r:id="rId9" display="https://leetcode.cn/problems/binary-tree-zigzag-level-order-traversal/solution/103-er-cha-shu-ju-zhi-xing-by-wywy-m-uxik/" xr:uid="{27BA8CEA-865C-FF4A-86D9-856D77C5ECBD}"/>
-    <hyperlink ref="A24" r:id="rId10" display="https://leetcode.cn/problems/basic-calculator/solution/by-wywy-m-543m/" xr:uid="{FA0221D9-1E03-FE40-A140-39F06F45E467}"/>
-    <hyperlink ref="A25" r:id="rId11" display="https://leetcode.cn/problems/largest-rectangle-in-histogram/solution/by-wywy-m-jel3/" xr:uid="{290D5E6D-B3ED-C24B-872D-1F93EDCDC189}"/>
-    <hyperlink ref="A16" r:id="rId12" display="https://leetcode.cn/problems/simplify-path/solution/71-jian-hua-lu-jing-by-wywy-m-tfon/" xr:uid="{A2E65B04-5214-9F4A-80C0-5308AC2FCD68}"/>
-    <hyperlink ref="A26" r:id="rId13" display="https://leetcode.cn/problems/basic-calculator-ii/solution/227-by-wywy-m-c9pw/" xr:uid="{F3C43D19-BBDE-5A4D-ACD9-A5C2FE96FA3C}"/>
-    <hyperlink ref="A17" r:id="rId14" display="https://leetcode.cn/problems/longest-well-performing-interval/solution/by-wywy-m-iqfn/" xr:uid="{917A0AFF-2AB6-0149-B6F0-1BB06C14C2A8}"/>
-    <hyperlink ref="A18" r:id="rId15" display="https://leetcode.cn/problems/evaluate-reverse-polish-notation/solution/150-by-wywy-m-mard/" xr:uid="{B23D8A99-CC93-224F-B1D4-FB2FFE806ED9}"/>
-    <hyperlink ref="A19" r:id="rId16" display="https://leetcode.cn/problems/minimum-insertions-to-balance-a-parentheses-string/solution/-by-wywy-m-4zuq/" xr:uid="{1F3D3135-F250-1A41-A6F7-217409CD1074}"/>
-    <hyperlink ref="A20" r:id="rId17" display="https://leetcode.cn/problems/minimum-add-to-make-parentheses-valid/solution/921-by-wywy-m-g9p3/" xr:uid="{98532AF3-6F3B-0544-BD97-1FC77AD12F32}"/>
-    <hyperlink ref="A21" r:id="rId18" display="https://leetcode.cn/problems/design-phone-directory/solution/379-by-wywy-m-pcgg/" xr:uid="{912F70F9-8FED-4844-AA1E-8E9331F43B4F}"/>
-    <hyperlink ref="A22" r:id="rId19" display="https://leetcode.cn/problems/score-of-parentheses/solution/856-gua-hao-de-fen-shu-stack-by-ywrx-5and/" xr:uid="{16E42127-27EF-1446-8A15-E551F6EBB563}"/>
-    <hyperlink ref="A6" r:id="rId20" display="https://leetcode.cn/problems/backspace-string-compare/solution/844-bi-jiao-han-tui-ge-de-zi-fu-chuan-st-0xc7/" xr:uid="{67DCDB62-41ED-404A-B6D6-918D50A0EA63}"/>
-    <hyperlink ref="A27" r:id="rId21" xr:uid="{F7D66BB5-D385-A748-90A8-5170E61B545A}"/>
-    <hyperlink ref="A28" r:id="rId22" xr:uid="{B94F7F45-0C42-9749-9646-3A1CE1D18EF6}"/>
-    <hyperlink ref="A29" r:id="rId23" xr:uid="{24579073-6DD8-2E4A-8745-FD3B694E6954}"/>
-    <hyperlink ref="A30" r:id="rId24" xr:uid="{F8886BAF-906E-DE42-9871-149A2F18FA70}"/>
-    <hyperlink ref="A31" r:id="rId25" xr:uid="{74931912-759E-A041-803B-A71EB8AF5159}"/>
-    <hyperlink ref="A32" r:id="rId26" xr:uid="{924746E3-2A6B-AE4A-9759-B162DD5A3FEC}"/>
+    <hyperlink ref="A9" r:id="rId1" display="https://leetcode.cn/problems/minimum-remove-to-make-valid-parentheses/solution/by-wywy-m-2t35/" xr:uid="{2EB1CF24-787A-924C-91DB-549CF776B0A3}"/>
+    <hyperlink ref="A10" r:id="rId2" display="https://leetcode.cn/problems/decode-string/solution/-by-wywy-m-lwwt/" xr:uid="{5D178BBF-6035-EF43-BDB9-401CBA123DDE}"/>
+    <hyperlink ref="A22" r:id="rId3" display="https://leetcode.cn/problems/minimize-deviation-in-array/solution/by-wywy-m-d6vv/" xr:uid="{E2C0663E-46FC-F44F-A9DE-3B2A01CCE254}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/next-greater-element-i/solution/-by-wywy-m-kp32/" xr:uid="{1635017B-5E04-0C45-A816-7E5A4EC696E1}"/>
+    <hyperlink ref="A11" r:id="rId5" display="https://leetcode.cn/problems/daily-temperatures/solution/739-mei-ri-wen-du-dan-diao-zhan-by-wywy-p1tl2/" xr:uid="{3B9663B1-07C0-A449-A8A8-8B3DA416A5B6}"/>
+    <hyperlink ref="A12" r:id="rId6" display="https://leetcode.cn/problems/remove-all-adjacent-duplicates-in-string-ii/solution/-by-wywy-m-g883/" xr:uid="{87237311-64CB-414E-A007-E3D64354DEE2}"/>
+    <hyperlink ref="A13" r:id="rId7" display="https://leetcode.cn/problems/add-two-numbers-ii/solution/by-wywy-m-kr74/" xr:uid="{E4C9551A-9B0F-3044-9E93-3D2801442FA6}"/>
+    <hyperlink ref="A14" r:id="rId8" display="https://leetcode.cn/problems/binary-tree-zigzag-level-order-traversal/solution/103-er-cha-shu-ju-zhi-xing-by-wywy-m-uxik/" xr:uid="{27BA8CEA-865C-FF4A-86D9-856D77C5ECBD}"/>
+    <hyperlink ref="A23" r:id="rId9" display="https://leetcode.cn/problems/basic-calculator/solution/by-wywy-m-543m/" xr:uid="{FA0221D9-1E03-FE40-A140-39F06F45E467}"/>
+    <hyperlink ref="A24" r:id="rId10" display="https://leetcode.cn/problems/largest-rectangle-in-histogram/solution/by-wywy-m-jel3/" xr:uid="{290D5E6D-B3ED-C24B-872D-1F93EDCDC189}"/>
+    <hyperlink ref="A15" r:id="rId11" display="https://leetcode.cn/problems/simplify-path/solution/71-jian-hua-lu-jing-by-wywy-m-tfon/" xr:uid="{A2E65B04-5214-9F4A-80C0-5308AC2FCD68}"/>
+    <hyperlink ref="A25" r:id="rId12" display="https://leetcode.cn/problems/basic-calculator-ii/solution/227-by-wywy-m-c9pw/" xr:uid="{F3C43D19-BBDE-5A4D-ACD9-A5C2FE96FA3C}"/>
+    <hyperlink ref="A16" r:id="rId13" display="https://leetcode.cn/problems/longest-well-performing-interval/solution/by-wywy-m-iqfn/" xr:uid="{917A0AFF-2AB6-0149-B6F0-1BB06C14C2A8}"/>
+    <hyperlink ref="A17" r:id="rId14" display="https://leetcode.cn/problems/evaluate-reverse-polish-notation/solution/150-by-wywy-m-mard/" xr:uid="{B23D8A99-CC93-224F-B1D4-FB2FFE806ED9}"/>
+    <hyperlink ref="A18" r:id="rId15" display="https://leetcode.cn/problems/minimum-insertions-to-balance-a-parentheses-string/solution/-by-wywy-m-4zuq/" xr:uid="{1F3D3135-F250-1A41-A6F7-217409CD1074}"/>
+    <hyperlink ref="A19" r:id="rId16" display="https://leetcode.cn/problems/minimum-add-to-make-parentheses-valid/solution/921-by-wywy-m-g9p3/" xr:uid="{98532AF3-6F3B-0544-BD97-1FC77AD12F32}"/>
+    <hyperlink ref="A20" r:id="rId17" display="https://leetcode.cn/problems/design-phone-directory/solution/379-by-wywy-m-pcgg/" xr:uid="{912F70F9-8FED-4844-AA1E-8E9331F43B4F}"/>
+    <hyperlink ref="A21" r:id="rId18" display="https://leetcode.cn/problems/score-of-parentheses/solution/856-gua-hao-de-fen-shu-stack-by-ywrx-5and/" xr:uid="{16E42127-27EF-1446-8A15-E551F6EBB563}"/>
+    <hyperlink ref="A6" r:id="rId19" display="https://leetcode.cn/problems/backspace-string-compare/solution/844-bi-jiao-han-tui-ge-de-zi-fu-chuan-st-0xc7/" xr:uid="{67DCDB62-41ED-404A-B6D6-918D50A0EA63}"/>
+    <hyperlink ref="A26" r:id="rId20" xr:uid="{F7D66BB5-D385-A748-90A8-5170E61B545A}"/>
+    <hyperlink ref="A27" r:id="rId21" xr:uid="{B94F7F45-0C42-9749-9646-3A1CE1D18EF6}"/>
+    <hyperlink ref="A28" r:id="rId22" xr:uid="{24579073-6DD8-2E4A-8745-FD3B694E6954}"/>
+    <hyperlink ref="A29" r:id="rId23" xr:uid="{F8886BAF-906E-DE42-9871-149A2F18FA70}"/>
+    <hyperlink ref="A30" r:id="rId24" xr:uid="{74931912-759E-A041-803B-A71EB8AF5159}"/>
+    <hyperlink ref="A31" r:id="rId25" xr:uid="{924746E3-2A6B-AE4A-9759-B162DD5A3FEC}"/>
+    <hyperlink ref="A32" r:id="rId26" display="https://leetcode.cn/problems/max-stack/solution/716-zui-da-zhan-by-wywy-m-pfny/" xr:uid="{5AEDDC01-03BF-4549-958C-252D6B8531CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8667,7 +8685,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C38DCB7-D208-4A47-A52C-374E9CD57FFC}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="75.33203125" style="10" customWidth="1"/>
@@ -9136,6 +9154,17 @@
       </c>
       <c r="C42" s="10">
         <v>20250719</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="10">
+        <v>20250823</v>
       </c>
     </row>
   </sheetData>
@@ -9180,6 +9209,7 @@
     <hyperlink ref="A40" r:id="rId35" xr:uid="{04785873-4BDF-2C4F-9B49-0979DE807FBD}"/>
     <hyperlink ref="A41" r:id="rId36" xr:uid="{39C352BC-02CC-B64F-BBA4-2D978CE750A4}"/>
     <hyperlink ref="A42" r:id="rId37" xr:uid="{8F285B38-2D86-BA45-8427-9B3EFAAC58E0}"/>
+    <hyperlink ref="A43" r:id="rId38" xr:uid="{224A5226-4AE2-A242-A7CF-2EFA5ABFC541}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9785,7 +9815,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAA87E2-0C96-3045-BD9E-C5C85205F434}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.33203125" style="6" customWidth="1"/>
@@ -9992,6 +10022,17 @@
       </c>
       <c r="C18" s="6">
         <v>20250721</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="7">
+        <v>20250823</v>
       </c>
     </row>
   </sheetData>
@@ -10016,6 +10057,7 @@
     <hyperlink ref="A16" r:id="rId15" xr:uid="{CBFBF69D-7CE2-0943-91D7-4BB1286A5EDC}"/>
     <hyperlink ref="A17" r:id="rId16" xr:uid="{331EC6DD-E2C5-6E47-BBAD-0BBA050507AA}"/>
     <hyperlink ref="A18" r:id="rId17" xr:uid="{78274215-8135-934A-A277-E6C94E09DFE7}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{26960301-6C1F-6547-83EC-B9B1CA0291A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2908EE7-685C-0640-9F3B-499E16B74F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC38A29-5091-EF4A-A9D3-388C0EC8E8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28760" windowHeight="17280" firstSheet="5" activeTab="18" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="-20" yWindow="760" windowWidth="28760" windowHeight="17280" firstSheet="5" activeTab="13" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="525">
   <si>
     <t>#</t>
   </si>
@@ -1626,6 +1626,9 @@
   </si>
   <si>
     <t>364 嵌套列表加权和II</t>
+  </si>
+  <si>
+    <t>360 有序转化数组</t>
   </si>
 </sst>
 </file>
@@ -4299,7 +4302,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F31A8D-9C09-434F-A40A-68C34FD0E968}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.83203125" style="10" customWidth="1"/>
@@ -4661,6 +4664,17 @@
       </c>
       <c r="C33" s="10">
         <v>20250126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="10">
+        <v>20250824</v>
       </c>
     </row>
   </sheetData>
@@ -4695,6 +4709,7 @@
     <hyperlink ref="A32" r:id="rId25" xr:uid="{81522808-E615-5241-AA06-184B31D238A1}"/>
     <hyperlink ref="A33" r:id="rId26" xr:uid="{099DEDFF-943D-F84A-A4DE-06653C3F6B2C}"/>
     <hyperlink ref="A6" r:id="rId27" display="https://leetcode.cn/post-editor/solution/create/?submissionId=602946873" xr:uid="{92E389EC-DC9F-0B42-907B-4E6D18E7A4B4}"/>
+    <hyperlink ref="A34" r:id="rId28" xr:uid="{D1907539-4F2C-8647-BB48-58DAAC431249}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10107"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC38A29-5091-EF4A-A9D3-388C0EC8E8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04284C6-8E3C-4E44-A777-CB76FC4573CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="28760" windowHeight="17280" firstSheet="5" activeTab="13" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" activeTab="6" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="524">
   <si>
     <t>#</t>
   </si>
@@ -1626,9 +1626,6 @@
   </si>
   <si>
     <t>364 嵌套列表加权和II</t>
-  </si>
-  <si>
-    <t>360 有序转化数组</t>
   </si>
 </sst>
 </file>
@@ -4302,7 +4299,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F31A8D-9C09-434F-A40A-68C34FD0E968}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.83203125" style="10" customWidth="1"/>
@@ -4664,17 +4661,6 @@
       </c>
       <c r="C33" s="10">
         <v>20250126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="10">
-        <v>20250824</v>
       </c>
     </row>
   </sheetData>
@@ -4709,7 +4695,6 @@
     <hyperlink ref="A32" r:id="rId25" xr:uid="{81522808-E615-5241-AA06-184B31D238A1}"/>
     <hyperlink ref="A33" r:id="rId26" xr:uid="{099DEDFF-943D-F84A-A4DE-06653C3F6B2C}"/>
     <hyperlink ref="A6" r:id="rId27" display="https://leetcode.cn/post-editor/solution/create/?submissionId=602946873" xr:uid="{92E389EC-DC9F-0B42-907B-4E6D18E7A4B4}"/>
-    <hyperlink ref="A34" r:id="rId28" xr:uid="{D1907539-4F2C-8647-BB48-58DAAC431249}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6804,15 +6789,9 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="7">
-        <v>20250823</v>
-      </c>
+      <c r="A32" s="8"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C27">
@@ -6844,7 +6823,6 @@
     <hyperlink ref="A29" r:id="rId23" xr:uid="{F8886BAF-906E-DE42-9871-149A2F18FA70}"/>
     <hyperlink ref="A30" r:id="rId24" xr:uid="{74931912-759E-A041-803B-A71EB8AF5159}"/>
     <hyperlink ref="A31" r:id="rId25" xr:uid="{924746E3-2A6B-AE4A-9759-B162DD5A3FEC}"/>
-    <hyperlink ref="A32" r:id="rId26" display="https://leetcode.cn/problems/max-stack/solution/716-zui-da-zhan-by-wywy-m-pfny/" xr:uid="{5AEDDC01-03BF-4549-958C-252D6B8531CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC38A29-5091-EF4A-A9D3-388C0EC8E8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D675EA-879C-2944-960D-FDA64D981BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="28760" windowHeight="17280" firstSheet="5" activeTab="13" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28760" windowHeight="17280" firstSheet="5" activeTab="6" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04284C6-8E3C-4E44-A777-CB76FC4573CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B2BF60-D136-0E47-BECA-E6DE0538C6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" activeTab="6" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" firstSheet="5" activeTab="18" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -5254,15 +5254,6 @@
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="10">
-        <v>20230623</v>
-      </c>
       <c r="E51" s="14"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -5357,22 +5348,21 @@
     <hyperlink ref="A49" r:id="rId32" xr:uid="{9F4002CE-364B-494E-B6AB-EFEC92EB2918}"/>
     <hyperlink ref="A26" r:id="rId33" xr:uid="{ED5D89E9-76CF-A048-BD72-F0BA151EEC9F}"/>
     <hyperlink ref="A50" r:id="rId34" xr:uid="{2236CD92-7436-3046-B2AB-2A201C581542}"/>
-    <hyperlink ref="A51" r:id="rId35" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
-    <hyperlink ref="A12" r:id="rId36" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
-    <hyperlink ref="A52" r:id="rId37" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
-    <hyperlink ref="A27" r:id="rId38" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
-    <hyperlink ref="A53" r:id="rId39" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
-    <hyperlink ref="A28" r:id="rId40" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
-    <hyperlink ref="A31" r:id="rId41" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
-    <hyperlink ref="A15" r:id="rId42" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
-    <hyperlink ref="A29" r:id="rId43" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
-    <hyperlink ref="A30" r:id="rId44" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
-    <hyperlink ref="A11" r:id="rId45" xr:uid="{89528EDA-A621-6D4D-A2DD-9DE18BC8A31E}"/>
-    <hyperlink ref="A56" r:id="rId46" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
-    <hyperlink ref="A32" r:id="rId47" xr:uid="{8AF59068-3701-144D-866B-DF434B216EEE}"/>
-    <hyperlink ref="A33" r:id="rId48" xr:uid="{CBACF588-0969-4A43-8A15-7D5C7F053B5C}"/>
-    <hyperlink ref="A34" r:id="rId49" xr:uid="{97AE6A05-E848-194F-99D0-CB202FE98A50}"/>
-    <hyperlink ref="A35" r:id="rId50" xr:uid="{25A08FC5-3ECE-2242-BBE5-070B267F3C14}"/>
+    <hyperlink ref="A12" r:id="rId35" xr:uid="{789116A2-DA3B-5146-B1CF-9CE94AFA59AE}"/>
+    <hyperlink ref="A52" r:id="rId36" xr:uid="{A1DEAF25-CFE6-0C43-8A67-63D1DD128370}"/>
+    <hyperlink ref="A27" r:id="rId37" display="1345 跳跃游戏" xr:uid="{16850ACC-824B-1D40-8830-CE4B42221DA3}"/>
+    <hyperlink ref="A53" r:id="rId38" xr:uid="{6E4A025A-11FC-B041-9FC6-D009B8C26B37}"/>
+    <hyperlink ref="A28" r:id="rId39" xr:uid="{9C0F05F6-4254-4140-8AA9-345AE0F6C457}"/>
+    <hyperlink ref="A31" r:id="rId40" xr:uid="{ACFB182A-5C8E-6542-B781-7EDA0648840C}"/>
+    <hyperlink ref="A15" r:id="rId41" xr:uid="{F9931DCB-71CA-5E47-B53D-4A6864353ED0}"/>
+    <hyperlink ref="A29" r:id="rId42" xr:uid="{11FEAA43-79D0-F544-BFD7-9C304540F746}"/>
+    <hyperlink ref="A30" r:id="rId43" xr:uid="{96D0E884-EC3F-1240-816E-8A1EDC3FAE42}"/>
+    <hyperlink ref="A11" r:id="rId44" xr:uid="{89528EDA-A621-6D4D-A2DD-9DE18BC8A31E}"/>
+    <hyperlink ref="A56" r:id="rId45" xr:uid="{70C72BD6-5530-F34C-B7E9-3E3790DAE81C}"/>
+    <hyperlink ref="A32" r:id="rId46" xr:uid="{8AF59068-3701-144D-866B-DF434B216EEE}"/>
+    <hyperlink ref="A33" r:id="rId47" xr:uid="{CBACF588-0969-4A43-8A15-7D5C7F053B5C}"/>
+    <hyperlink ref="A34" r:id="rId48" xr:uid="{97AE6A05-E848-194F-99D0-CB202FE98A50}"/>
+    <hyperlink ref="A35" r:id="rId49" xr:uid="{25A08FC5-3ECE-2242-BBE5-070B267F3C14}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5381,7 +5371,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F10A632-C78C-6347-8E5A-4720E264DA34}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="82" style="10" customWidth="1"/>
@@ -5729,6 +5719,17 @@
       </c>
       <c r="C31" s="10">
         <v>20250722</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="10">
+        <v>20250909</v>
       </c>
     </row>
   </sheetData>
@@ -5766,6 +5767,7 @@
     <hyperlink ref="A29" r:id="rId28" xr:uid="{DF19D5B2-DD91-FE43-9464-1009CFE3AF36}"/>
     <hyperlink ref="A30" r:id="rId29" display="1306 跳跃游戏" xr:uid="{B4339213-63EF-E54E-87E9-20B533BF7F44}"/>
     <hyperlink ref="A31" r:id="rId30" xr:uid="{B7B72A55-6E11-C344-86D7-730B25BA5254}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{E2609709-3CD3-3648-9A1F-188186BE2B3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6336,7 +6338,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="7">
-        <v>20220823</v>
+        <v>20250909</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B2BF60-D136-0E47-BECA-E6DE0538C6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508D3E8A-2754-394A-9319-DEC4918F6BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" firstSheet="5" activeTab="18" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" firstSheet="10" activeTab="11" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508D3E8A-2754-394A-9319-DEC4918F6BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BFA265-5DC8-5C49-B291-DCE5850FD08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" firstSheet="10" activeTab="11" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" activeTab="6" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="528">
   <si>
     <t>#</t>
   </si>
@@ -1626,6 +1626,18 @@
   </si>
   <si>
     <t>364 嵌套列表加权和II</t>
+  </si>
+  <si>
+    <t>1448 Count Good Nodes in Binary Tree</t>
+  </si>
+  <si>
+    <t>489 Robot Room Cleaner</t>
+  </si>
+  <si>
+    <t>409 Longest Palindorme</t>
+  </si>
+  <si>
+    <t>1676 Lowest Common Ancestor of a Binary Tree IV</t>
   </si>
 </sst>
 </file>
@@ -5254,6 +5266,15 @@
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="10">
+        <v>20250919</v>
+      </c>
       <c r="E51" s="14"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -5363,6 +5384,7 @@
     <hyperlink ref="A33" r:id="rId47" xr:uid="{CBACF588-0969-4A43-8A15-7D5C7F053B5C}"/>
     <hyperlink ref="A34" r:id="rId48" xr:uid="{97AE6A05-E848-194F-99D0-CB202FE98A50}"/>
     <hyperlink ref="A35" r:id="rId49" xr:uid="{25A08FC5-3ECE-2242-BBE5-070B267F3C14}"/>
+    <hyperlink ref="A51" r:id="rId50" xr:uid="{C99B0E18-EDA8-9D4F-BA44-0DA3957D211E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7738,7 +7760,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A9675C-39F8-DD4C-B84E-2CBC8BF054BB}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="65.6640625" style="10" customWidth="1"/>
@@ -8129,7 +8151,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="7">
-        <v>20250122</v>
+        <v>20251019</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -8327,7 +8349,7 @@
         <v>5</v>
       </c>
       <c r="C54" s="10">
-        <v>20250122</v>
+        <v>20251019</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -8339,6 +8361,28 @@
       </c>
       <c r="C55" s="10">
         <v>20250421</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="10">
+        <v>20251019</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="10">
+        <v>20251020</v>
       </c>
     </row>
   </sheetData>
@@ -8385,6 +8429,8 @@
     <hyperlink ref="A54" r:id="rId37" xr:uid="{23504A27-82D3-7141-94CB-F17A82D6A7EF}"/>
     <hyperlink ref="A55" r:id="rId38" xr:uid="{8B2B0486-5360-9745-A744-589A7CCFC882}"/>
     <hyperlink ref="A13" r:id="rId39" xr:uid="{DB5E8E4D-CC40-9D47-951E-0B84D4FB4309}"/>
+    <hyperlink ref="A56" r:id="rId40" xr:uid="{3E12CFD2-D04E-F14E-8E20-9E6402873634}"/>
+    <hyperlink ref="A57" r:id="rId41" xr:uid="{26CAF446-E8B5-804E-B7C1-E59B268AF274}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -9450,7 +9496,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="7">
-        <v>20230403</v>
+        <v>20251020</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -9552,14 +9598,14 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
-        <v>409</v>
+      <c r="A3" s="8" t="s">
+        <v>526</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>4</v>
+      <c r="C3" s="7">
+        <v>20251019</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -9803,6 +9849,7 @@
     <hyperlink ref="A21" r:id="rId14" xr:uid="{834553C4-6D16-1D49-A51B-1DD0CE9585E5}"/>
     <hyperlink ref="A22" r:id="rId15" xr:uid="{26AEC0E4-FF45-724E-A3DF-74F32AB3E1A4}"/>
     <hyperlink ref="A23" r:id="rId16" xr:uid="{E96EB736-57C9-3B44-AB07-6300ED324D4A}"/>
+    <hyperlink ref="A3" r:id="rId17" xr:uid="{51BF2B55-ECAB-D446-8C0D-EB08424E4AAE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10107"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuwang/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BFA265-5DC8-5C49-B291-DCE5850FD08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F6B2E-28A9-E341-94D0-05AE8C86BC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28760" windowHeight="15920" activeTab="6" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="1980" windowWidth="28760" windowHeight="15920" firstSheet="3" activeTab="16" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="533">
   <si>
     <t>#</t>
   </si>
@@ -1638,6 +1638,21 @@
   </si>
   <si>
     <t>1676 Lowest Common Ancestor of a Binary Tree IV</t>
+  </si>
+  <si>
+    <t>272 Closest Binary Search Tree Value II</t>
+  </si>
+  <si>
+    <t>152 Maximum Product Subarray</t>
+  </si>
+  <si>
+    <t>244 Shortest Word Distance II</t>
+  </si>
+  <si>
+    <t>156 Binary Tree Upside Down</t>
+  </si>
+  <si>
+    <t>671 Second Minimum Node In a Binary Tree</t>
   </si>
 </sst>
 </file>
@@ -2529,7 +2544,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87904762-BFEC-434E-9C53-A84DD8444479}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.33203125" style="6" customWidth="1"/>
@@ -2800,6 +2815,17 @@
       </c>
       <c r="C24" s="6">
         <v>20250521</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="6">
+        <v>20251112</v>
       </c>
     </row>
   </sheetData>
@@ -2824,6 +2850,7 @@
     <hyperlink ref="A10" r:id="rId15" xr:uid="{9C812532-9B74-F245-9727-E6278385A520}"/>
     <hyperlink ref="A11" r:id="rId16" xr:uid="{B75B3B15-223A-154E-B443-CA5C70F537A6}"/>
     <hyperlink ref="A7" r:id="rId17" xr:uid="{7BC51ED3-D8F0-4E4C-AE63-756A29B376C2}"/>
+    <hyperlink ref="A25" r:id="rId18" xr:uid="{F1A0FD55-F377-A542-99FE-614B17D1C32C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2940,7 +2967,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF52CBDF-A54F-B64B-ABC7-BC9DA66EFACF}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" style="10" customWidth="1"/>
@@ -3717,6 +3744,17 @@
       </c>
       <c r="C70" s="10">
         <v>20250720</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="10">
+        <v>20251112</v>
       </c>
     </row>
   </sheetData>
@@ -3783,6 +3821,7 @@
     <hyperlink ref="A68" r:id="rId57" xr:uid="{E80A8A71-063F-A44D-8B00-EB348F17438D}"/>
     <hyperlink ref="A69" r:id="rId58" xr:uid="{4712E19F-E9AB-EB41-88EA-1E0F711FE97E}"/>
     <hyperlink ref="A70" r:id="rId59" xr:uid="{5A9FFCE5-A402-3347-BE28-0BA8C267259D}"/>
+    <hyperlink ref="A71" r:id="rId60" xr:uid="{F0253633-05A0-1F4B-98F4-DAC44EFFA677}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4311,7 +4350,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F31A8D-9C09-434F-A40A-68C34FD0E968}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.83203125" style="10" customWidth="1"/>
@@ -4673,6 +4712,17 @@
       </c>
       <c r="C33" s="10">
         <v>20250126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="10">
+        <v>20251114</v>
       </c>
     </row>
   </sheetData>
@@ -4707,6 +4757,7 @@
     <hyperlink ref="A32" r:id="rId25" xr:uid="{81522808-E615-5241-AA06-184B31D238A1}"/>
     <hyperlink ref="A33" r:id="rId26" xr:uid="{099DEDFF-943D-F84A-A4DE-06653C3F6B2C}"/>
     <hyperlink ref="A6" r:id="rId27" display="https://leetcode.cn/post-editor/solution/create/?submissionId=602946873" xr:uid="{92E389EC-DC9F-0B42-907B-4E6D18E7A4B4}"/>
+    <hyperlink ref="A34" r:id="rId28" xr:uid="{543B7F13-D5F5-AE46-883B-9171CD2FD5F8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5531,7 +5582,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="7">
-        <v>20220820</v>
+        <v>20251115</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -5946,7 +5997,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="7">
-        <v>20230225</v>
+        <v>20251115</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -7353,7 +7404,7 @@
     <hyperlink ref="A6" r:id="rId5" display="https://leetcode.cn/problems/design-browser-history/solution/-by-wywy-m-brat/" xr:uid="{DBCEC44C-0FF3-754F-9624-0182F8A06912}"/>
     <hyperlink ref="A9" r:id="rId6" display="https://leetcode.cn/problems/max-stack/solution/716-zui-da-zhan-by-wywy-m-pfny/" xr:uid="{631B774A-E844-AC42-AEC9-BF62CADD2598}"/>
     <hyperlink ref="A7" r:id="rId7" display="https://leetcode-cn.com/problems/lru-cache/solution/146-lru-by-wywy-m-zu1k/" xr:uid="{4317DAE7-DDBA-954E-B9D0-6C938FC2CDB7}"/>
-    <hyperlink ref="A8" r:id="rId8" display="https://leetcode.cn/problems/flatten-nested-list-iterator/solution/341-bian-ping-hua-qian-tao-lie-biao-die-9hkzc/" xr:uid="{698A819F-9708-2146-AD46-F61F59C8B741}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{698A819F-9708-2146-AD46-F61F59C8B741}"/>
     <hyperlink ref="A10" r:id="rId9" xr:uid="{1284FA53-A548-C248-A9C4-413BC0013767}"/>
     <hyperlink ref="A11" r:id="rId10" xr:uid="{5C8B9003-5BEC-D34B-97A5-D14B96CF7B14}"/>
   </hyperlinks>
@@ -7583,7 +7634,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C589BEE-21A2-4E43-9E3C-F419C25A1E80}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24.83203125" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.5" style="10" customWidth="1"/>
@@ -7668,6 +7719,17 @@
         <v>20250712</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10">
+        <v>20251115</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://leetcode-cn.com/problems/integer-to-english-words/solution/273-zheng-shu-zhuan-huan-ying-wen-biao-s-d9es/" xr:uid="{6A706088-D403-F94C-894B-198211511F89}"/>
@@ -7676,6 +7738,7 @@
     <hyperlink ref="A5" r:id="rId4" display="https://leetcode.cn/problems/integer-to-english-words/solution/by-wywy-m-4yer/" xr:uid="{4208DCE0-2370-3C48-8A98-BD04CF3C5890}"/>
     <hyperlink ref="A6" r:id="rId5" xr:uid="{D2B24540-D3F4-BB42-AE97-BDB45B74E404}"/>
     <hyperlink ref="A7" r:id="rId6" xr:uid="{3DCD20F0-4E25-584B-B97C-5A305AC259D8}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{1A1B453B-31CF-3A44-9D92-BDA18B647E00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7891,14 +7954,14 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>671</v>
+      <c r="A12" s="7" t="s">
+        <v>532</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>4</v>
+      <c r="C12" s="7">
+        <v>20251115</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">

--- a/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
+++ b/Algorithms/Leetcode/Leetcode Catalog - Yu Wang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/Desktop/MyStudyNotes/Algorithms/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41F6B2E-28A9-E341-94D0-05AE8C86BC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF78702-B3E0-4B48-8185-1551ACBB7CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1980" windowWidth="28760" windowHeight="15920" firstSheet="3" activeTab="16" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
+    <workbookView xWindow="0" yWindow="1980" windowWidth="28760" windowHeight="15920" activeTab="6" xr2:uid="{D74CB876-27C2-064D-BD73-4428B59FF732}"/>
   </bookViews>
   <sheets>
     <sheet name="Array" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="534">
   <si>
     <t>#</t>
   </si>
@@ -1653,6 +1653,9 @@
   </si>
   <si>
     <t>671 Second Minimum Node In a Binary Tree</t>
+  </si>
+  <si>
+    <t>450 Delete Node in a BST</t>
   </si>
 </sst>
 </file>
@@ -8666,14 +8669,14 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
-        <v>450</v>
+      <c r="A15" s="8" t="s">
+        <v>533</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>4</v>
+      <c r="C15" s="7">
+        <v>20251118</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -8782,6 +8785,7 @@
     <hyperlink ref="A23" r:id="rId11" xr:uid="{00D1453D-6A79-6E42-90D5-9FAE60DE038A}"/>
     <hyperlink ref="A13" r:id="rId12" xr:uid="{C80453CE-42E5-D44A-87A9-FCD34B080B26}"/>
     <hyperlink ref="A4" r:id="rId13" xr:uid="{A8A58163-A5F7-AB45-A522-5E41E86C0C2A}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{A5E2B0F0-EC87-F04C-B40A-00F6BDC32E7E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
